--- a/currentbuild/all-profiles.xlsx
+++ b/currentbuild/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-12T11:23:40+00:00</t>
+    <t>2023-02-13T09:41:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/all-profiles.xlsx
+++ b/currentbuild/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-08T20:17:08+00:00</t>
+    <t>2024-01-12T06:32:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/all-profiles.xlsx
+++ b/currentbuild/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.0</t>
+    <t>0.8.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-11T18:58:49+00:00</t>
+    <t>2024-03-12T11:58:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/all-profiles.xlsx
+++ b/currentbuild/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-17T09:59:20+00:00</t>
+    <t>2024-04-06T16:49:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>HL7 Norway (https://github.com/HL7Norway)</t>
   </si>
   <si>
     <t>Description</t>
